--- a/08_tarimsal_girdi_fiyat_endeksi/Veri.xlsx
+++ b/08_tarimsal_girdi_fiyat_endeksi/Veri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ertugrultuti/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82511F6-9858-6948-AF4B-E976391F0BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5615103A-69D4-5340-AC81-FA25CDD04B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
